--- a/author.xlsx
+++ b/author.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5214F717-7945-466A-96B1-D73D21E396B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="2580" yWindow="1488" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -12,10 +13,21 @@
     <sheet name="Student 2" sheetId="2" r:id="rId3"/>
     <sheet name="Student 3" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -24,9 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="52">
   <si>
-    <t>&lt;Project Name&gt;</t>
-  </si>
-  <si>
     <t>Short Description</t>
   </si>
   <si>
@@ -177,13 +186,16 @@
     <t>e-mail university</t>
   </si>
   <si>
-    <t>&lt;name of the github project&gt;</t>
+    <t>CNC Hot Wire Foam Cutter</t>
+  </si>
+  <si>
+    <t>HotWire</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -539,35 +551,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="31.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -583,279 +598,279 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" customWidth="1"/>
+    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1">
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
         <v>9</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A44" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
         <v>20</v>
       </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
         <v>24</v>
-      </c>
-      <c r="B50" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -863,277 +878,277 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1">
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
         <v>9</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A44" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
         <v>20</v>
       </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
         <v>24</v>
-      </c>
-      <c r="B50" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0200-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1142,277 +1157,277 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1">
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
         <v>9</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A44" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
         <v>20</v>
       </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
         <v>24</v>
-      </c>
-      <c r="B50" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0300-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,17 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5214F717-7945-466A-96B1-D73D21E396B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F999F8C-C744-4AAA-AF2D-457619ED69BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="1488" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6585" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
-    <sheet name="Student 1" sheetId="1" r:id="rId2"/>
-    <sheet name="Student 2" sheetId="2" r:id="rId3"/>
-    <sheet name="Student 3" sheetId="3" r:id="rId4"/>
+    <sheet name="Alexandra Roth" sheetId="1" r:id="rId2"/>
+    <sheet name="David Atrops" sheetId="2" r:id="rId3"/>
+    <sheet name="Dennis Smirnow" sheetId="7" r:id="rId4"/>
+    <sheet name="Leon Ronge" sheetId="8" r:id="rId5"/>
+    <sheet name="Samuel Drees" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="85">
   <si>
     <t>Short Description</t>
   </si>
@@ -57,24 +59,12 @@
     <t>Street home:</t>
   </si>
   <si>
-    <t>&lt;Steinweg 15&gt;</t>
-  </si>
-  <si>
     <t>City home:</t>
   </si>
   <si>
-    <t>&lt;26723 Emden&gt;</t>
-  </si>
-  <si>
     <t>Company name/Department:</t>
   </si>
   <si>
-    <t>&lt;Hochschule Emden/Leer&gt; or &lt; VW Wolfsburg&gt; or &lt;...&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Fachbereich Technik&gt;  or &lt;Strak&gt; or &lt;...&gt;</t>
-  </si>
-  <si>
     <t>Street Workplace:</t>
   </si>
   <si>
@@ -120,12 +110,6 @@
     <t>Matrikelnumber</t>
   </si>
   <si>
-    <t>Wings</t>
-  </si>
-  <si>
-    <t>Elmar</t>
-  </si>
-  <si>
     <t>Study Course:</t>
   </si>
   <si>
@@ -138,39 +122,21 @@
     <t>CPs:</t>
   </si>
   <si>
-    <t xml:space="preserve"> &lt;5&gt; or &lt;10&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Mechanical Engineering Department&gt;</t>
-  </si>
-  <si>
     <t>Constantiaplatz 4</t>
   </si>
   <si>
     <t xml:space="preserve">Home: </t>
   </si>
   <si>
-    <t>&lt;04921 123 456&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Study: </t>
   </si>
   <si>
-    <t>&lt;04921 807 1429&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Workplace: </t>
   </si>
   <si>
-    <t>&lt;04921 807 1428&gt;</t>
-  </si>
-  <si>
     <t>Name, Surname</t>
   </si>
   <si>
-    <t>The nice project is…</t>
-  </si>
-  <si>
     <t>Name of the module:</t>
   </si>
   <si>
@@ -190,13 +156,149 @@
   </si>
   <si>
     <t>HotWire</t>
+  </si>
+  <si>
+    <t>ELMAR ist ein CNC-gesteuerter Heißdrahtschneider zum Schneiden von Styropor. Die Maschine wird über einen Arduino Uno mit GRBL-Firmware gesteuert und über den Universal G-Code Sender (UGS) vom Laptop aus bedient. Dabei werden vorhandene G-Code-Dateien an die Steuerung übertragen, sodass der erhitzte Draht automatisch entlang der vorgegebenen Kontur verfährt und das Material schneidet.
+Das Projekt umfasst den mechanischen Aufbau, die elektrische Verdrahtung, die Einrichtung der Steuerungssoftware sowie die Durchführung von Funktionstests. Ziel ist es, eine funktionsfähige und nachvollziehbar dokumentierte CNC-Schneidemaschine für einfache Styroporschnitte zu entwickeln.</t>
+  </si>
+  <si>
+    <t>Drees</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>Fachbereich Technik</t>
+  </si>
+  <si>
+    <t>Maschinenbau und Design (B.Eng.)</t>
+  </si>
+  <si>
+    <t>Hochschule Emden/Leer</t>
+  </si>
+  <si>
+    <t>26723 Emden</t>
+  </si>
+  <si>
+    <t>Ronge</t>
+  </si>
+  <si>
+    <t>Leon</t>
+  </si>
+  <si>
+    <t>0176 43688291</t>
+  </si>
+  <si>
+    <t>01575 5182081</t>
+  </si>
+  <si>
+    <t>0176 9561178</t>
+  </si>
+  <si>
+    <t>01573 8225483</t>
+  </si>
+  <si>
+    <t>0176 21533814</t>
+  </si>
+  <si>
+    <t>Roth</t>
+  </si>
+  <si>
+    <t>Alexandra</t>
+  </si>
+  <si>
+    <t>Fliederstraße 1</t>
+  </si>
+  <si>
+    <t>26506 Norden</t>
+  </si>
+  <si>
+    <t>Alexandra.roth@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>Alexandra.roth04@web.de</t>
+  </si>
+  <si>
+    <t>alex.rxth</t>
+  </si>
+  <si>
+    <t>Oststraße 11</t>
+  </si>
+  <si>
+    <t>40764 Langenfeld (Rheinland)</t>
+  </si>
+  <si>
+    <t>david.adrian.atrops@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">david.atrops@stud.hs-emden-leer.de, </t>
+  </si>
+  <si>
+    <t>DivadSporta</t>
+  </si>
+  <si>
+    <t>Atrops</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Smirnow</t>
+  </si>
+  <si>
+    <t>Dennis</t>
+  </si>
+  <si>
+    <t>shinichidc</t>
+  </si>
+  <si>
+    <t>dennis.smirnow@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>dennis.smirnow98@gmail.com</t>
+  </si>
+  <si>
+    <t>Klein-von-Diepoldstraße.23</t>
+  </si>
+  <si>
+    <t>26721 Emden</t>
+  </si>
+  <si>
+    <t>Auricher-Straße 135</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 26721 Emden</t>
+  </si>
+  <si>
+    <t>leon.ronge@stud.hs-Emden-Leer.de</t>
+  </si>
+  <si>
+    <t>1567_hdvwio_03145</t>
+  </si>
+  <si>
+    <t>leonronge@t-online.de</t>
+  </si>
+  <si>
+    <t>Südstraße 11</t>
+  </si>
+  <si>
+    <t>57638 Neitersen</t>
+  </si>
+  <si>
+    <t>s43sdree@gmail.com</t>
+  </si>
+  <si>
+    <t>samuel.drees@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>sam44523</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +338,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -254,10 +364,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -272,8 +383,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -553,38 +666,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="31.5546875" customWidth="1"/>
+    <col min="3" max="3" width="31.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="33.6" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:3" ht="33.4" x14ac:dyDescent="1">
       <c r="A1" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -600,269 +713,273 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="47.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="33.109375" customWidth="1"/>
-    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35.796875" customWidth="1"/>
+    <col min="3" max="3" width="33.1328125" customWidth="1"/>
+    <col min="4" max="4" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.85">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>7025637</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1">
-        <v>45351</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1">
-        <v>45594</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="B19" s="1">
+        <v>38023</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A37" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
-      <c r="A37" s="5" t="s">
+      <c r="B40" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A44" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B50" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
-      <c r="A44" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -880,269 +997,272 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.59765625" customWidth="1"/>
+    <col min="3" max="3" width="15.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.85">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>7013979</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1">
-        <v>45351</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1">
-        <v>45594</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="B19" s="1">
+        <v>36525</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A37" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
-      <c r="A37" s="5" t="s">
+      <c r="B40" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A44" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B50" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
-      <c r="A44" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1152,66 +1272,649 @@
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{F0FF9304-9743-4FFB-A398-90638137B788}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A2440C-15CA-43E8-999D-D1F8F76E65E1}">
+  <dimension ref="A3:F50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="34.53125" customWidth="1"/>
+    <col min="2" max="2" width="41.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.1328125" customWidth="1"/>
+    <col min="4" max="5" width="16.1328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.85">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="2">
+        <v>7023434</v>
+      </c>
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A37" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A44" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{9D088768-5C90-4D05-84DB-BDC1923BD05C}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{AF81092A-3B40-42A2-8254-F6C56B3896DB}">
+      <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{356D6C17-35C1-4C6D-A8F4-7CA36F076175}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{13B3073B-FB09-4267-AB9A-4A7BB2D27385}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75A98E7-1097-4B1F-A33F-4BBAE74538AD}">
+  <dimension ref="A3:F50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="31.73046875" customWidth="1"/>
+    <col min="2" max="2" width="42.33203125" customWidth="1"/>
+    <col min="3" max="3" width="33.1328125" customWidth="1"/>
+    <col min="4" max="4" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.85">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2">
+        <v>7026641</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="1">
+        <v>35834</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A37" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A44" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{433E5093-20CD-4C1D-8AFF-1543B2E8EFC1}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{C252B114-0074-49A5-8E6A-383B42080305}">
+      <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.85">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>7026354</v>
+      </c>
+      <c r="D5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1219,209 +1922,203 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1">
-        <v>45351</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1">
-        <v>45594</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="B19" s="1">
+        <v>36830</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="B23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A37" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.4">
-      <c r="A37" s="5" t="s">
+      <c r="B40" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
+      <c r="A44" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B50" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.4">
-      <c r="A44" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1431,6 +2128,9 @@
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{03B76011-BC5F-4887-B456-423E068407D4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/author.xlsx
+++ b/author.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F999F8C-C744-4AAA-AF2D-457619ED69BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6177A135-D801-446B-8E3E-8D8CBA16AA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6585" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="86">
   <si>
     <t>Short Description</t>
   </si>
@@ -77,22 +77,10 @@
     <t>Supervisor workplace:</t>
   </si>
   <si>
-    <t>&lt;Einstein, Albert&gt;</t>
-  </si>
-  <si>
-    <t>&lt;00494921 807-1001&gt;</t>
-  </si>
-  <si>
     <t>Email:</t>
   </si>
   <si>
-    <t>&lt;albert.einstein@hs-emden-leer.de&gt;</t>
-  </si>
-  <si>
     <t>Second examiner:</t>
-  </si>
-  <si>
-    <t>&lt;Prof. Dr. Carla Columna&gt;</t>
   </si>
   <si>
     <t>Outstanding examinations:</t>
@@ -292,6 +280,21 @@
   </si>
   <si>
     <t>sam44523</t>
+  </si>
+  <si>
+    <t>elmar.wings@hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Elmar Wings</t>
+  </si>
+  <si>
+    <t>malena.wilken@hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>Malena Wilken</t>
+  </si>
+  <si>
+    <t>Unbekannt</t>
   </si>
 </sst>
 </file>
@@ -377,13 +380,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -672,11 +675,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="33.4" x14ac:dyDescent="1">
-      <c r="A1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="A1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
@@ -684,20 +687,20 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
+      <c r="A5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -729,42 +732,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2">
         <v>7025637</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -772,7 +775,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -785,7 +791,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1">
         <v>46091</v>
@@ -793,7 +799,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1">
         <v>46196</v>
@@ -801,12 +807,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -830,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
@@ -838,7 +844,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
@@ -846,17 +852,17 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
@@ -864,7 +870,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
@@ -872,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
@@ -882,20 +888,20 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
@@ -908,10 +914,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
@@ -919,15 +925,15 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
@@ -941,15 +947,15 @@
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A44" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
@@ -957,15 +963,15 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
@@ -976,17 +982,14 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1012,42 +1015,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C5" s="2">
         <v>7013979</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -1055,7 +1058,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -1068,7 +1074,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1">
         <v>46091</v>
@@ -1076,7 +1082,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1">
         <v>46196</v>
@@ -1084,12 +1090,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1113,7 +1119,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
@@ -1121,7 +1127,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
@@ -1129,17 +1135,17 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
@@ -1147,7 +1153,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
@@ -1155,7 +1161,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
@@ -1165,20 +1171,20 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
@@ -1191,10 +1197,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
@@ -1202,15 +1208,15 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
@@ -1224,15 +1230,15 @@
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A44" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
@@ -1240,15 +1246,15 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
@@ -1259,18 +1265,15 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0200-000000000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0200-000001000000}">
-      <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="F5" r:id="rId1" xr:uid="{F0FF9304-9743-4FFB-A398-90638137B788}"/>
@@ -1297,42 +1300,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2">
         <v>7023434</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -1340,7 +1343,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -1353,7 +1359,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1">
         <v>46091</v>
@@ -1361,7 +1367,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1">
         <v>46196</v>
@@ -1369,12 +1375,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1398,7 +1404,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
@@ -1406,7 +1412,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
@@ -1414,17 +1420,17 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
@@ -1432,7 +1438,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
@@ -1440,7 +1446,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
@@ -1450,20 +1456,20 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
@@ -1476,10 +1482,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
@@ -1487,15 +1493,15 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
@@ -1509,15 +1515,15 @@
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A44" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
@@ -1525,15 +1531,15 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
@@ -1544,18 +1550,15 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{9D088768-5C90-4D05-84DB-BDC1923BD05C}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{AF81092A-3B40-42A2-8254-F6C56B3896DB}">
-      <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="E5" r:id="rId1" xr:uid="{356D6C17-35C1-4C6D-A8F4-7CA36F076175}"/>
@@ -1585,42 +1588,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2">
         <v>7026641</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -1628,7 +1631,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -1641,7 +1647,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1">
         <v>46091</v>
@@ -1649,7 +1655,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1">
         <v>46196</v>
@@ -1657,12 +1663,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1686,7 +1692,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
@@ -1694,7 +1700,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
@@ -1702,17 +1708,17 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
@@ -1720,7 +1726,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
@@ -1728,7 +1734,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
@@ -1738,20 +1744,20 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
@@ -1764,10 +1770,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
@@ -1775,15 +1781,15 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
@@ -1797,15 +1803,15 @@
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A44" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
@@ -1813,15 +1819,15 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
@@ -1832,18 +1838,15 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{433E5093-20CD-4C1D-8AFF-1543B2E8EFC1}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{C252B114-0074-49A5-8E6A-383B42080305}">
-      <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1868,42 +1871,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2">
         <v>7026354</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -1911,7 +1914,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -1924,7 +1930,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1">
         <v>46091</v>
@@ -1932,7 +1938,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1">
         <v>46196</v>
@@ -1940,12 +1946,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -1969,7 +1975,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
@@ -1977,7 +1983,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
@@ -1985,17 +1991,17 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
@@ -2003,7 +2009,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
@@ -2011,7 +2017,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
@@ -2021,20 +2027,20 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
@@ -2047,10 +2053,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
@@ -2058,15 +2064,15 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
@@ -2080,15 +2086,15 @@
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.65">
       <c r="A44" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
@@ -2096,15 +2102,15 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
@@ -2115,18 +2121,15 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0300-000000000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0300-000001000000}">
-      <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="F5" r:id="rId1" xr:uid="{03B76011-BC5F-4887-B456-423E068407D4}"/>
